--- a/Assets/Data/Heroics.xlsx
+++ b/Assets/Data/Heroics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Heroics" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
   <si>
     <t>Id</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>盲目</t>
+  </si>
+  <si>
+    <t>花粉症</t>
   </si>
 </sst>
 </file>
@@ -277,10 +280,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -311,7 +314,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,10 +366,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,46 +380,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -392,9 +396,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -409,22 +420,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -432,9 +427,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,8 +441,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -463,7 +466,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,7 +508,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,13 +538,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,31 +598,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,31 +634,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,73 +646,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -657,17 +660,52 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -687,32 +725,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -730,27 +753,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -762,145 +765,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -929,12 +932,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1239,8 +1242,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="11.8181818181818" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -2897,6 +2903,27 @@
         <v>1</v>
       </c>
       <c r="F79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>2390</v>
+      </c>
+      <c r="B80">
+        <v>2390</v>
+      </c>
+      <c r="C80" t="str">
+        <f>INDEX(TextData!B:B,MATCH(A80,TextData!A:A))</f>
+        <v>花粉症</v>
+      </c>
+      <c r="D80">
+        <v>-4</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
         <v>8</v>
       </c>
     </row>
@@ -2909,7 +2936,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="51.3636363636364" customWidth="1"/>
@@ -3573,6 +3600,14 @@
         <v>84</v>
       </c>
     </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>2390</v>
+      </c>
+      <c r="B80" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
